--- a/cat1_code.xlsx
+++ b/cat1_code.xlsx
@@ -25,7 +25,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="DejaVu Sans"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">类别</t>
@@ -35,6 +35,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
     </r>
@@ -45,6 +46,7 @@
         <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">类别</t>
     </r>
@@ -53,6 +55,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
     </r>
@@ -61,6 +64,7 @@
         <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">编码</t>
     </r>
@@ -69,67 +73,67 @@
     <t xml:space="preserve">加长轴转子加工</t>
   </si>
   <si>
-    <t xml:space="preserve">C01</t>
+    <t xml:space="preserve">A</t>
   </si>
   <si>
     <t xml:space="preserve">同步电机</t>
   </si>
   <si>
-    <t xml:space="preserve">C02</t>
+    <t xml:space="preserve">B</t>
   </si>
   <si>
     <t xml:space="preserve">机座</t>
   </si>
   <si>
-    <t xml:space="preserve">C03</t>
+    <t xml:space="preserve">C</t>
   </si>
   <si>
     <t xml:space="preserve">特殊电机装配</t>
   </si>
   <si>
-    <t xml:space="preserve">C04</t>
+    <t xml:space="preserve">D</t>
   </si>
   <si>
     <t xml:space="preserve">端盖</t>
   </si>
   <si>
-    <t xml:space="preserve">C05</t>
+    <t xml:space="preserve">E</t>
   </si>
   <si>
     <t xml:space="preserve">绕嵌排</t>
   </si>
   <si>
-    <t xml:space="preserve">C06</t>
+    <t xml:space="preserve">F</t>
   </si>
   <si>
     <t xml:space="preserve">装配</t>
   </si>
   <si>
-    <t xml:space="preserve">C07</t>
+    <t xml:space="preserve">G</t>
   </si>
   <si>
     <t xml:space="preserve">装配铁</t>
   </si>
   <si>
-    <t xml:space="preserve">C08</t>
+    <t xml:space="preserve">H</t>
   </si>
   <si>
     <t xml:space="preserve">转子</t>
   </si>
   <si>
-    <t xml:space="preserve">C09</t>
+    <t xml:space="preserve">I</t>
   </si>
   <si>
     <t xml:space="preserve">轴</t>
   </si>
   <si>
-    <t xml:space="preserve">C10</t>
+    <t xml:space="preserve">J</t>
   </si>
   <si>
     <t xml:space="preserve">轴转子</t>
   </si>
   <si>
-    <t xml:space="preserve">C11</t>
+    <t xml:space="preserve">K</t>
   </si>
 </sst>
 </file>
@@ -144,6 +148,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -162,18 +167,20 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="DejaVu Sans"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -249,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -259,7 +266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -267,7 +274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -275,7 +282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -283,7 +290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -291,7 +298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -299,7 +306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -307,7 +314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -315,7 +322,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -323,7 +330,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -331,7 +338,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -339,7 +346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
